--- a/05_ai-policy-architecture/exercises/starter/ai_aup.xlsx
+++ b/05_ai-policy-architecture/exercises/starter/ai_aup.xlsx
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -597,50 +597,64 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Draft a complete, enforceable AI AUP across six sheets (AUP Body, Prohibited Uses, Acceptable Uses, Exception Procedure, Control Map). Pre-filled rows on every sheet show the worked pattern. Cross-reference the Policy Stack Reference sheet (read-only) for out-of-scope cases.</t>
+          <t>Draft a complete, enforceable AI AUP across six working sheets (AUP Body, Prohibited Uses, Acceptable Uses, Exception Procedure, Control Map, Policy Stack Reference — last sheet is read-only). Pre-filled rows on every sheet show the worked pattern. Cross-reference the Policy Stack Reference sheet (read-only) for out-of-scope cases.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>REASONING NOTE:</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>For every cell where you fill in `[Your response here]`, append a short rationale on a new line in the same cell, formatted as: Reasoning: &lt;one sentence on why this control / definition / clause is the right choice&gt;. This rationale lives inside the same cell as the answer (use Alt+Enter / Option+Enter for a soft line break). It is part of the deliverable — graders look for it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>COLOR LEGEND:</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>Blue Header — Sheet / column headers</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Green — Scenario information</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Light Blue — Pre-filled context / worked example rows</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Pink — Student work areas — fill these cells</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Yellow — Reference / rubric (read-only)</t>
         </is>
@@ -712,7 +726,7 @@
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>[Your response here — write the section body. See pre-filled sections 1.0 / 4.0 for tone and depth.]</t>
+          <t>[Your response here — write the Scope section body following the pattern of pre-filled Section 1.0 / 4.0. Cover: who the AUP binds (employees, contractors, partners), where it applies (company devices, networks, data), the Scenario Brief's three in-scope use cases, and what's explicitly out-of-scope (handed off to the other three policies in the stack).]</t>
         </is>
       </c>
     </row>
@@ -729,7 +743,7 @@
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here — write the section body. See pre-filled sections 1.0 / 4.0 for tone and depth.]</t>
+          <t>[Your response here — write the Definitions section body following the pattern of pre-filled Section 1.0 / 4.0. Define the key terms the rest of the policy depends on: AI tool, public vs. sanctioned AI tool, AI coding assistant, MNPI, customer financial data, regulated codebase — each in one short sentence.]</t>
         </is>
       </c>
     </row>
@@ -843,12 +857,12 @@
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — explain WHY this is prohibited. Tie the rationale to a specific risk channel (e.g., leakage of proprietary/regulated code into a vendor training corpus) and reference the configuration-level fix that makes the in-policy version acceptable. Match the depth of rows 2-3.]</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — define a tiered 1st / 2nd / 3rd offense consequence ladder. Calibrate severity to the actor (developer / tool admin) and include retraining, access revocation, and termination tiers consistent with rows 2-3.]</t>
         </is>
       </c>
     </row>
@@ -863,12 +877,12 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — explain WHY embedded AI features in third-party SaaS are risky even when the host tool is sanctioned. Address unknown prompt retention, lack of security review, and the gap between tool-level and feature-level approval. Match the depth of rows 2-3.]</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — define a tiered 1st / 2nd / 3rd offense consequence ladder. Consider escalating against the user-administrator role (who enabled the feature) rather than the underlying tool. Match rows 2-3.]</t>
         </is>
       </c>
     </row>
@@ -883,12 +897,12 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — explain WHY AI output cannot stand alone for an investment / trade / compliance decision affecting a client. Tie to fiduciary duty, hallucination/bias risk, and the regulator's expectation of a named accountable human. Match the depth of rows 2-3.]</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — define a tiered 1st / 2nd / 3rd offense consequence ladder. Include trading-authorization suspension and a regulatory disclosure review at the top tier, mirroring the customer-data ladder in row 2.]</t>
         </is>
       </c>
     </row>
@@ -969,7 +983,7 @@
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — describe the verification step a user or manager performs to confirm this use is in-policy. Name the specific corpus / list / configuration check (e.g., source-corpus check, 'already published' filter, sanctioned-tool list lookup). Match rows 2-3.]</t>
         </is>
       </c>
     </row>
@@ -984,7 +998,7 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — describe the verification step the user performs BEFORE enabling the AI feature. Name a two-part check: a tool-level check (feature on the Sanctioned-Tools list) AND a content-level check (meeting / document owner confirms no MNPI or customer financial data). Match rows 2-3.]</t>
         </is>
       </c>
     </row>
@@ -999,7 +1013,7 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — describe the verification step that gates this drafting use. Apply a content-classification check on BOTH the prompt and the AI's output (e.g., the 'could this be shared externally as-is?' test), and require the same internal-document review the draft would otherwise get. Match rows 2-3.]</t>
         </is>
       </c>
     </row>
@@ -1113,22 +1127,22 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — describe what happens in the Risk Acceptance step: which role reviews mitigations, what they check them against (hint: another sheet in this workbook), and the special handling for MNPI-Adjacent requests.]</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the role(s) that own this step. The default is a risk function, with a legal/compliance co-sign required for MNPI-Adjacent requests.]</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — give a tiered SLA (faster for Elevated / MNPI-Adjacent than for Standard), in business days. Pattern matches the triage SLA in row 3.]</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the artifact this step produces (e.g., a signed memo) and call out an explicit MNPI determination when applicable.]</t>
         </is>
       </c>
     </row>
@@ -1140,22 +1154,22 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — describe the final approval decision and which approver acts at each tier (Standard vs. Elevated vs. MNPI-Adjacent). Reference the AI Review Board defined in AUP Body Section 4.0.]</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the approver(s) by role. Standard tier can be a CISO designate; higher tiers escalate to the AI Review Board.]</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — give a tiered SLA: a fixed business-day window for Standard, and a session-based cadence for Elevated / MNPI-Adjacent (e.g., next AIRB meeting).]</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the artifact: a signed exception record that MUST carry an explicit expiry date (critical for the next step).]</t>
         </is>
       </c>
     </row>
@@ -1167,22 +1181,22 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — describe what happens at expiry: hard-stop default, requester options (close out vs. re-request), and a stricter rule for MNPI-Adjacent exceptions (e.g., auto-close, fresh AIRB review required).]</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the role(s) that drive the expiry / re-review (requester + an operational owner that tracks the expiry queue).]</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — give a default expiry window plus a shorter maximum for MNPI-Adjacent exceptions.]</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the artifact: an expiry notice plus the closeout or re-request ticket that proves the exception did not silently roll forward.]</t>
         </is>
       </c>
     </row>
@@ -1295,17 +1309,17 @@
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the detective control that would catch this. Think about WHERE in the developer workflow the binding check lives (e.g., a CI/CD gate, an IDE-telemetry check, a per-codebase 'do not train' flag) so non-compliance blocks merge.]</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the role that OWNS this control end-to-end (an engineering or developer-tooling leader, not the AUP owner).]</t>
         </is>
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — give the control's current state. Use one of: Live / Partial / Planned, and add a short qualifier if Partial / Planned (e.g., what backlog or rollout is outstanding). Match rows 2-3.]</t>
         </is>
       </c>
     </row>
@@ -1320,17 +1334,17 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the detective control. Think about a procurement-side gate plus an SSO-admin-layer enforcement that disables AI features on tools not in the Tool Inventory.]</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the role(s) that own this control. Likely shared between an IT/SSO administrator and Procurement.]</t>
         </is>
       </c>
       <c r="E5" s="16" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — give the control's current state. Use Live / Partial / Planned and call out any vendor-review backlog if Partial.]</t>
         </is>
       </c>
     </row>
@@ -1345,17 +1359,17 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the detective control. Think about a workflow-level enforcement where AI output is captured as evidence but cannot itself complete the customer-affecting action without a human approval step.]</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the role that owns this control (a business-line operations leader, not the security team).]</t>
         </is>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — give the control's current state (Live / Partial / Planned). Match rows 2-3.]</t>
         </is>
       </c>
     </row>

--- a/05_ai-policy-architecture/exercises/starter/ai_aup.xlsx
+++ b/05_ai-policy-architecture/exercises/starter/ai_aup.xlsx
@@ -1100,7 +1100,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Security Operations triages the request — confirms the form is complete, classifies as Standard / Elevated / MNPI-Adjacent. MNPI-Adjacent requests skip directly to step 4.</t>
+          <t>Security Operations triages the request — confirms the form is complete, classifies as Standard / Elevated / MNPI-Adjacent. MNPI-Adjacent requests proceed through the full workflow, with GC co-signature required at the Risk Acceptance step.</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
